--- a/responses_adults.xlsx
+++ b/responses_adults.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uab-my.sharepoint.com/personal/1218423_uab_cat/Documents/Research/BiLS/Scripts/presentation_portugal/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="13_ncr:1_{72059464-D85A-534D-BDB5-B02CD405C606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{951D2B62-9608-412E-B184-BF3094BA8BE0}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{72059464-D85A-534D-BDB5-B02CD405C606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2AA40D83-882C-4155-B641-1D64DA1A03AF}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="105">
   <si>
     <t>Marca de temps</t>
   </si>
@@ -363,6 +363,15 @@
   <si>
     <t>UPF_019</t>
   </si>
+  <si>
+    <t>Baix Penedès</t>
+  </si>
+  <si>
+    <t>Badajoz</t>
+  </si>
+  <si>
+    <t>Córdoba</t>
+  </si>
 </sst>
 </file>
 
@@ -371,7 +380,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm:ss"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -391,6 +400,12 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -413,7 +428,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -422,6 +437,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2435,6 +2454,93 @@
       <c r="C18" s="3" t="s">
         <v>97</v>
       </c>
+      <c r="D18" s="5">
+        <v>20</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M18" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="N18" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="O18" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="P18" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q18" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="R18" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="S18" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="T18" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="U18" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="V18" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="W18" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="X18" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y18" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z18" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA18" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB18" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC18" s="5">
+        <v>2005</v>
+      </c>
+      <c r="AD18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF18" s="5" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="19" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
@@ -2443,6 +2549,93 @@
       <c r="C19" s="3" t="s">
         <v>96</v>
       </c>
+      <c r="D19" s="5">
+        <v>21</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="M19" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="N19" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="O19" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="P19" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q19" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="R19" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="S19" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="T19" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="U19" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="V19" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="W19" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="X19" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y19" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="Z19" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA19" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="AB19" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="AC19" s="5">
+        <v>2005</v>
+      </c>
+      <c r="AD19" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AE19" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF19" s="5" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="20" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="3" t="s">
@@ -2450,6 +2643,89 @@
       </c>
       <c r="C20" s="3" t="s">
         <v>96</v>
+      </c>
+      <c r="D20" s="5">
+        <v>23</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="M20" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="N20" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="O20" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="P20" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q20" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="R20" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="S20" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="T20" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="U20" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="V20" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="W20" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="X20" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y20" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z20" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA20" s="4"/>
+      <c r="AB20" s="4"/>
+      <c r="AC20" s="5">
+        <v>2003</v>
+      </c>
+      <c r="AD20" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE20" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF20" s="5" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
